--- a/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
+++ b/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwiegner\PycharmProjects\AdOpT_DAC-Offshore\dac_offshore\clean_data\technologies_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7C7090-4892-42A5-AFF8-9ADD71AFF5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D24750F-34C7-4616-9712-703932F086BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$F$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="106">
   <si>
     <t>offshore_new</t>
   </si>
@@ -352,6 +352,12 @@
   </si>
   <si>
     <t>co2storage</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Too far away for DAC</t>
   </si>
 </sst>
 </file>
@@ -711,15 +717,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -735,8 +741,11 @@
       <c r="E1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -747,7 +756,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -758,7 +767,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -769,7 +778,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -783,7 +792,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -797,7 +806,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -811,7 +820,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -825,7 +834,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -839,7 +848,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -853,7 +862,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -867,7 +876,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -881,7 +890,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -895,7 +904,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -905,11 +914,11 @@
       <c r="C14" t="s">
         <v>64</v>
       </c>
-      <c r="E14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -923,7 +932,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -937,7 +946,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -951,7 +960,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -965,7 +974,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -976,7 +985,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -987,7 +996,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -998,7 +1007,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1009,7 +1018,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1020,7 +1029,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1031,7 +1040,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1042,7 +1051,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -1056,7 +1065,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1067,7 +1076,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -1081,7 +1090,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
@@ -1095,7 +1104,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1123,7 +1132,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1137,7 +1146,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -1151,7 +1160,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -1179,7 +1188,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -1193,7 +1202,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
@@ -1207,7 +1216,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
@@ -1221,7 +1230,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -1235,7 +1244,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -1249,7 +1258,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1263,7 +1272,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -1277,7 +1286,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -1291,7 +1300,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1305,7 +1314,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1319,7 +1328,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1333,7 +1342,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -1361,7 +1370,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -1375,7 +1384,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -1389,7 +1398,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -1403,7 +1412,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -1417,7 +1426,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -1431,7 +1440,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>41</v>
       </c>
@@ -1445,7 +1454,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -1459,7 +1468,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>43</v>
       </c>
@@ -1474,11 +1483,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E38" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E56">
-      <sortCondition ref="B1:B38"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:F56" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
@@ -1492,13 +1497,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4641E15-13AD-4645-88BC-55D8D2E876ED}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -1510,7 +1515,7 @@
         <v>'RE_only': 'RE only',</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1522,7 +1527,7 @@
         <v>'Battery_on': 'Battery (onshore only)',</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1534,7 +1539,7 @@
         <v>'Battery_off': 'Battery (offshore only)',</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1546,7 +1551,7 @@
         <v>'Battery_all': 'Battery (all)',</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1558,7 +1563,7 @@
         <v>'ElectricityGrid_all': 'Grid Expansion (all)',</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1570,7 +1575,7 @@
         <v>'Hydrogen_Baseline': 'Hydrogen (all)',</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -1582,7 +1587,7 @@
         <v>'Hydrogen_H1': 'Hydrogen (no storage)',</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -1594,7 +1599,7 @@
         <v>'Hydrogen_H2': 'Hydrogen (no hydrogen offshore)',</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>74</v>
       </c>
@@ -1606,7 +1611,7 @@
         <v>'Hydrogen_H3': 'Hydrogen (no hydrogen onshore)',</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -1618,7 +1623,7 @@
         <v>'Hydrogen_H4': 'Hydrogen (local use only)',</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1630,7 +1635,7 @@
         <v>'All': 'All Pathways',</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -1643,7 +1648,7 @@
         <v>'RE_only_no_onshore_wind': 'RE only - no onshore wind',</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -1656,7 +1661,7 @@
         <v>'Battery_on_no_onshore_wind': 'Battery (onshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>77</v>
       </c>
@@ -1669,7 +1674,7 @@
         <v>'Battery_off_no_onshore_wind': 'Battery (offshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -1682,7 +1687,7 @@
         <v>'Battery_all_no_onshore_wind': 'Battery (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1695,7 +1700,7 @@
         <v>'ElectricityGrid_all_no_onshore_wind': 'Grid Expansion (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -1708,7 +1713,7 @@
         <v>'Hydrogen_Baseline_no_onshore_wind': 'Hydrogen (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>78</v>
       </c>
@@ -1721,7 +1726,7 @@
         <v>'Hydrogen_H1_no_onshore_wind': 'Hydrogen (no storage) - no onshore wind',</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -1734,7 +1739,7 @@
         <v>'Hydrogen_H2_no_onshore_wind': 'Hydrogen (no hydrogen offshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -1747,7 +1752,7 @@
         <v>'Hydrogen_H3_no_onshore_wind': 'Hydrogen (no hydrogen onshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -1760,7 +1765,7 @@
         <v>'Hydrogen_H4_no_onshore_wind': 'Hydrogen (local use only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>65</v>
       </c>

--- a/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
+++ b/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/AdOpT-NET0_DAC-Offshore/dac_offshore/clean_data/technologies_new/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B970953-C56B-E842-9483-313AFEB9052B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5015D0B1-7877-A040-A4B4-98ADA7200B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="133">
+  <si>
+    <t>Electrolyser_PEM_offshore</t>
+  </si>
   <si>
     <t>offshore_new</t>
   </si>
@@ -186,6 +189,9 @@
     <t>All</t>
   </si>
   <si>
+    <t>Offshore_Wind</t>
+  </si>
+  <si>
     <t>UK_L</t>
   </si>
   <si>
@@ -228,18 +234,51 @@
     <t>DE_G</t>
   </si>
   <si>
+    <t>New_Offshore_Farms_2040</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV</t>
+  </si>
+  <si>
+    <t>UK_M</t>
+  </si>
+  <si>
+    <t>UK_O</t>
+  </si>
+  <si>
+    <t>UK_N</t>
+  </si>
+  <si>
+    <t>Electrolyser_PEM_offshore, Storage_Battery_Offshore</t>
+  </si>
+  <si>
     <t>Onshore_Wind, PV, Storage_Battery_new</t>
   </si>
   <si>
+    <t>Onshore_Wind, PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen, Storage_Battery_new</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, Electrolyser_PEM_offshore, Storage_Battery_Offshore</t>
+  </si>
+  <si>
     <t>RE_only</t>
   </si>
   <si>
     <t>Offshore_Wind, Storage_Battery_Offshore</t>
   </si>
   <si>
+    <t>Offshore_Wind, Electrolyser_PEM_offshore</t>
+  </si>
+  <si>
     <t>All_no_onshore_wind</t>
   </si>
   <si>
+    <t>PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen, Storage_Battery_new</t>
+  </si>
+  <si>
     <t>RE_only_no_onshore_wind</t>
   </si>
   <si>
@@ -252,6 +291,15 @@
     <t>Hydrogen_Baseline_no_onshore_wind</t>
   </si>
   <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>PV, Storage_Battery_new</t>
+  </si>
+  <si>
+    <t>PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
     <t>Battery_on</t>
   </si>
   <si>
@@ -270,6 +318,18 @@
     <t>Hydrogen_H4</t>
   </si>
   <si>
+    <t>Onshore_Wind, PV, Electrolyser_PEM, FuelCell</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
+    <t>PV, Electrolyser_PEM, FuelCell</t>
+  </si>
+  <si>
+    <t>PV, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
     <t>Battery_on_no_onshore_wind</t>
   </si>
   <si>
@@ -321,12 +381,30 @@
     <t>Hydrogen (local use only)</t>
   </si>
   <si>
+    <t>ElectricityGrid_on</t>
+  </si>
+  <si>
+    <t>ElectricityGrid_off</t>
+  </si>
+  <si>
+    <t>ElectricityGrid_noBorder</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
+  </si>
+  <si>
     <t>DK_ST1</t>
   </si>
   <si>
+    <t>New_CO2_Storage_2040</t>
+  </si>
+  <si>
     <t>NO_ST2</t>
   </si>
   <si>
+    <t>DK_ST2</t>
+  </si>
+  <si>
     <t>NO_ST1</t>
   </si>
   <si>
@@ -339,22 +417,28 @@
     <t>DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
   </si>
   <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
     <t>Offshore_DAC_only</t>
   </si>
   <si>
     <t>Onshore_DAC_only</t>
   </si>
   <si>
+    <t>Onshore_DAC_retrofits</t>
+  </si>
+  <si>
     <t>PermanentStorage_CO2_simple</t>
   </si>
   <si>
-    <t>No_DAC</t>
-  </si>
-  <si>
-    <t>co2storage</t>
-  </si>
-  <si>
-    <t>DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
+    <t>Offshore_Wind, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>RE_only_no_space</t>
   </si>
 </sst>
 </file>
@@ -429,28 +513,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -726,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:AE60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -743,842 +806,4482 @@
     <col min="24" max="24" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>89</v>
+      </c>
+      <c r="R1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U1" t="str">
+        <f>C1&amp;"_no_onshore_wind"</f>
+        <v>RE_only_no_onshore_wind</v>
+      </c>
+      <c r="V1" t="str">
+        <f>H1&amp;"_no_onshore_wind"</f>
+        <v>Battery_on_no_onshore_wind</v>
+      </c>
+      <c r="W1" t="str">
+        <f>I1&amp;"_no_onshore_wind"</f>
+        <v>Battery_off_no_onshore_wind</v>
+      </c>
+      <c r="X1" t="str">
+        <f>J1&amp;"_no_onshore_wind"</f>
+        <v>Battery_all_no_onshore_wind</v>
+      </c>
+      <c r="Y1" t="str">
+        <f>K1&amp;"_no_onshore_wind"</f>
+        <v>ElectricityGrid_all_no_onshore_wind</v>
+      </c>
+      <c r="Z1" t="str">
+        <f t="shared" ref="Z1:AE1" si="0">O1&amp;"_no_onshore_wind"</f>
+        <v>Hydrogen_Baseline_no_onshore_wind</v>
+      </c>
+      <c r="AA1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H1_no_onshore_wind</v>
+      </c>
+      <c r="AB1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H2_no_onshore_wind</v>
+      </c>
+      <c r="AC1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H3_no_onshore_wind</v>
+      </c>
+      <c r="AD1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H4_no_onshore_wind</v>
+      </c>
+      <c r="AE1" t="str">
+        <f t="shared" si="0"/>
+        <v>All_no_onshore_wind</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>57</v>
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>0</v>
+      </c>
+      <c r="T9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W9" t="s">
+        <v>45</v>
+      </c>
+      <c r="X9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
+        <v>69</v>
+      </c>
+      <c r="W10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>54</v>
+        <v>130</v>
+      </c>
+      <c r="F11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>69</v>
+      </c>
+      <c r="W11" t="s">
+        <v>45</v>
+      </c>
+      <c r="X11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>53</v>
+        <v>130</v>
+      </c>
+      <c r="F12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" t="s">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>69</v>
+      </c>
+      <c r="W12" t="s">
+        <v>45</v>
+      </c>
+      <c r="X12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" t="s">
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T13" t="s">
+        <v>69</v>
+      </c>
+      <c r="W13" t="s">
+        <v>45</v>
+      </c>
+      <c r="X13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="G14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>69</v>
+      </c>
+      <c r="W14" t="s">
+        <v>45</v>
+      </c>
+      <c r="X14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" t="s">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" t="s">
+        <v>69</v>
+      </c>
+      <c r="W15" t="s">
+        <v>45</v>
+      </c>
+      <c r="X15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>69</v>
+      </c>
+      <c r="W16" t="s">
+        <v>45</v>
+      </c>
+      <c r="X16" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" t="s">
+        <v>123</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
+        <v>69</v>
+      </c>
+      <c r="W17" t="s">
+        <v>45</v>
+      </c>
+      <c r="X17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
+        <v>69</v>
+      </c>
+      <c r="W18" t="s">
+        <v>45</v>
+      </c>
+      <c r="X18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>12</v>
+        <v>123</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" t="s">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
+        <v>69</v>
+      </c>
+      <c r="W19" t="s">
+        <v>45</v>
+      </c>
+      <c r="X19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>13</v>
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>0</v>
+      </c>
+      <c r="T20" t="s">
+        <v>69</v>
+      </c>
+      <c r="W20" t="s">
+        <v>45</v>
+      </c>
+      <c r="X20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" t="s">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
+        <v>0</v>
+      </c>
+      <c r="T21" t="s">
+        <v>69</v>
+      </c>
+      <c r="W21" t="s">
+        <v>45</v>
+      </c>
+      <c r="X21" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" t="s">
+        <v>123</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" t="s">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W22" t="s">
+        <v>45</v>
+      </c>
+      <c r="X22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O23" t="s">
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>0</v>
+      </c>
+      <c r="T23" t="s">
+        <v>69</v>
+      </c>
+      <c r="W23" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" t="s">
+        <v>70</v>
+      </c>
+      <c r="K24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" t="s">
+        <v>71</v>
+      </c>
+      <c r="P24" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>71</v>
+      </c>
+      <c r="R24" t="s">
+        <v>93</v>
+      </c>
+      <c r="S24" t="s">
+        <v>71</v>
+      </c>
+      <c r="T24" t="s">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s">
+        <v>83</v>
+      </c>
+      <c r="V24" t="s">
+        <v>84</v>
+      </c>
+      <c r="W24" t="s">
+        <v>83</v>
+      </c>
+      <c r="X24" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" t="s">
+        <v>70</v>
+      </c>
+      <c r="I25" t="s">
+        <v>65</v>
+      </c>
+      <c r="J25" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" t="s">
+        <v>71</v>
+      </c>
+      <c r="P25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>71</v>
+      </c>
+      <c r="R25" t="s">
+        <v>93</v>
+      </c>
+      <c r="S25" t="s">
+        <v>71</v>
+      </c>
+      <c r="T25" t="s">
+        <v>72</v>
+      </c>
+      <c r="U25" t="s">
+        <v>83</v>
+      </c>
+      <c r="V25" t="s">
+        <v>84</v>
+      </c>
+      <c r="W25" t="s">
+        <v>83</v>
+      </c>
+      <c r="X25" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" t="s">
+        <v>71</v>
+      </c>
+      <c r="P26" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>71</v>
+      </c>
+      <c r="R26" t="s">
+        <v>93</v>
+      </c>
+      <c r="S26" t="s">
+        <v>71</v>
+      </c>
+      <c r="T26" t="s">
+        <v>72</v>
+      </c>
+      <c r="U26" t="s">
+        <v>83</v>
+      </c>
+      <c r="V26" t="s">
+        <v>84</v>
+      </c>
+      <c r="W26" t="s">
+        <v>83</v>
+      </c>
+      <c r="X26" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>65</v>
+      </c>
+      <c r="N27" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" t="s">
+        <v>71</v>
+      </c>
+      <c r="P27" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>71</v>
+      </c>
+      <c r="R27" t="s">
+        <v>93</v>
+      </c>
+      <c r="S27" t="s">
+        <v>71</v>
+      </c>
+      <c r="T27" t="s">
+        <v>72</v>
+      </c>
+      <c r="U27" t="s">
+        <v>83</v>
+      </c>
+      <c r="V27" t="s">
+        <v>84</v>
+      </c>
+      <c r="W27" t="s">
+        <v>83</v>
+      </c>
+      <c r="X27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" t="s">
+        <v>65</v>
+      </c>
+      <c r="O28" t="s">
+        <v>71</v>
+      </c>
+      <c r="P28" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>71</v>
+      </c>
+      <c r="R28" t="s">
+        <v>93</v>
+      </c>
+      <c r="S28" t="s">
+        <v>71</v>
+      </c>
+      <c r="T28" t="s">
+        <v>72</v>
+      </c>
+      <c r="U28" t="s">
+        <v>83</v>
+      </c>
+      <c r="V28" t="s">
+        <v>84</v>
+      </c>
+      <c r="W28" t="s">
+        <v>83</v>
+      </c>
+      <c r="X28" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" t="s">
+        <v>70</v>
+      </c>
+      <c r="I29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P29" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" t="s">
+        <v>93</v>
+      </c>
+      <c r="S29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T29" t="s">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s">
+        <v>83</v>
+      </c>
+      <c r="V29" t="s">
+        <v>84</v>
+      </c>
+      <c r="W29" t="s">
+        <v>83</v>
+      </c>
+      <c r="X29" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" t="s">
+        <v>65</v>
+      </c>
+      <c r="O30" t="s">
+        <v>71</v>
+      </c>
+      <c r="P30" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30" t="s">
+        <v>93</v>
+      </c>
+      <c r="S30" t="s">
+        <v>71</v>
+      </c>
+      <c r="T30" t="s">
+        <v>72</v>
+      </c>
+      <c r="U30" t="s">
+        <v>83</v>
+      </c>
+      <c r="V30" t="s">
+        <v>84</v>
+      </c>
+      <c r="W30" t="s">
+        <v>83</v>
+      </c>
+      <c r="X30" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31" t="s">
+        <v>71</v>
+      </c>
+      <c r="P31" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>71</v>
+      </c>
+      <c r="R31" t="s">
+        <v>93</v>
+      </c>
+      <c r="S31" t="s">
+        <v>71</v>
+      </c>
+      <c r="T31" t="s">
+        <v>72</v>
+      </c>
+      <c r="U31" t="s">
+        <v>83</v>
+      </c>
+      <c r="V31" t="s">
+        <v>84</v>
+      </c>
+      <c r="W31" t="s">
+        <v>83</v>
+      </c>
+      <c r="X31" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32" t="s">
+        <v>71</v>
+      </c>
+      <c r="P32" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>71</v>
+      </c>
+      <c r="R32" t="s">
+        <v>93</v>
+      </c>
+      <c r="S32" t="s">
+        <v>71</v>
+      </c>
+      <c r="T32" t="s">
+        <v>72</v>
+      </c>
+      <c r="U32" t="s">
+        <v>83</v>
+      </c>
+      <c r="V32" t="s">
+        <v>84</v>
+      </c>
+      <c r="W32" t="s">
+        <v>83</v>
+      </c>
+      <c r="X32" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" t="s">
+        <v>70</v>
+      </c>
+      <c r="K33" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" t="s">
+        <v>65</v>
+      </c>
+      <c r="N33" t="s">
+        <v>65</v>
+      </c>
+      <c r="O33" t="s">
+        <v>71</v>
+      </c>
+      <c r="P33" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>71</v>
+      </c>
+      <c r="R33" t="s">
+        <v>93</v>
+      </c>
+      <c r="S33" t="s">
+        <v>71</v>
+      </c>
+      <c r="T33" t="s">
+        <v>72</v>
+      </c>
+      <c r="U33" t="s">
+        <v>83</v>
+      </c>
+      <c r="V33" t="s">
+        <v>84</v>
+      </c>
+      <c r="W33" t="s">
+        <v>83</v>
+      </c>
+      <c r="X33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" t="s">
+        <v>65</v>
+      </c>
+      <c r="O34" t="s">
+        <v>71</v>
+      </c>
+      <c r="P34" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>71</v>
+      </c>
+      <c r="R34" t="s">
+        <v>93</v>
+      </c>
+      <c r="S34" t="s">
+        <v>71</v>
+      </c>
+      <c r="T34" t="s">
+        <v>72</v>
+      </c>
+      <c r="U34" t="s">
+        <v>83</v>
+      </c>
+      <c r="V34" t="s">
+        <v>84</v>
+      </c>
+      <c r="W34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X34" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" t="s">
+        <v>70</v>
+      </c>
+      <c r="I35" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" t="s">
+        <v>65</v>
+      </c>
+      <c r="O35" t="s">
+        <v>71</v>
+      </c>
+      <c r="P35" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>71</v>
+      </c>
+      <c r="R35" t="s">
+        <v>93</v>
+      </c>
+      <c r="S35" t="s">
+        <v>71</v>
+      </c>
+      <c r="T35" t="s">
+        <v>72</v>
+      </c>
+      <c r="U35" t="s">
+        <v>83</v>
+      </c>
+      <c r="V35" t="s">
+        <v>84</v>
+      </c>
+      <c r="W35" t="s">
+        <v>83</v>
+      </c>
+      <c r="X35" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I36" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" t="s">
+        <v>70</v>
+      </c>
+      <c r="K36" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" t="s">
+        <v>65</v>
+      </c>
+      <c r="N36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O36" t="s">
+        <v>71</v>
+      </c>
+      <c r="P36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>71</v>
+      </c>
+      <c r="R36" t="s">
+        <v>93</v>
+      </c>
+      <c r="S36" t="s">
+        <v>71</v>
+      </c>
+      <c r="T36" t="s">
+        <v>72</v>
+      </c>
+      <c r="U36" t="s">
+        <v>83</v>
+      </c>
+      <c r="V36" t="s">
+        <v>84</v>
+      </c>
+      <c r="W36" t="s">
+        <v>83</v>
+      </c>
+      <c r="X36" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" t="s">
+        <v>65</v>
+      </c>
+      <c r="O37" t="s">
+        <v>71</v>
+      </c>
+      <c r="P37" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>71</v>
+      </c>
+      <c r="R37" t="s">
+        <v>93</v>
+      </c>
+      <c r="S37" t="s">
+        <v>71</v>
+      </c>
+      <c r="T37" t="s">
+        <v>72</v>
+      </c>
+      <c r="U37" t="s">
+        <v>83</v>
+      </c>
+      <c r="V37" t="s">
+        <v>84</v>
+      </c>
+      <c r="W37" t="s">
+        <v>83</v>
+      </c>
+      <c r="X37" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" t="s">
+        <v>65</v>
+      </c>
+      <c r="N38" t="s">
+        <v>65</v>
+      </c>
+      <c r="O38" t="s">
+        <v>71</v>
+      </c>
+      <c r="P38" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>71</v>
+      </c>
+      <c r="R38" t="s">
+        <v>93</v>
+      </c>
+      <c r="S38" t="s">
+        <v>71</v>
+      </c>
+      <c r="T38" t="s">
+        <v>72</v>
+      </c>
+      <c r="U38" t="s">
+        <v>83</v>
+      </c>
+      <c r="V38" t="s">
+        <v>84</v>
+      </c>
+      <c r="W38" t="s">
+        <v>83</v>
+      </c>
+      <c r="X38" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
-        <v>101</v>
-      </c>
-      <c r="E38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>116</v>
+      </c>
+      <c r="D39" t="s">
+        <v>65</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>116</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" t="s">
+        <v>70</v>
+      </c>
+      <c r="K39" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" t="s">
+        <v>65</v>
+      </c>
+      <c r="N39" t="s">
+        <v>65</v>
+      </c>
+      <c r="O39" t="s">
+        <v>71</v>
+      </c>
+      <c r="P39" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>71</v>
+      </c>
+      <c r="R39" t="s">
+        <v>93</v>
+      </c>
+      <c r="S39" t="s">
+        <v>71</v>
+      </c>
+      <c r="T39" t="s">
+        <v>72</v>
+      </c>
+      <c r="U39" t="s">
+        <v>83</v>
+      </c>
+      <c r="V39" t="s">
+        <v>84</v>
+      </c>
+      <c r="W39" t="s">
+        <v>83</v>
+      </c>
+      <c r="X39" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" t="s">
+        <v>49</v>
+      </c>
+      <c r="I40" t="s">
+        <v>75</v>
+      </c>
+      <c r="J40" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" t="s">
+        <v>49</v>
+      </c>
+      <c r="M40" t="s">
+        <v>49</v>
+      </c>
+      <c r="N40" t="s">
+        <v>49</v>
+      </c>
+      <c r="O40" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>49</v>
+      </c>
+      <c r="R40" t="s">
+        <v>76</v>
+      </c>
+      <c r="S40" t="s">
+        <v>49</v>
+      </c>
+      <c r="T40" t="s">
+        <v>73</v>
+      </c>
+      <c r="U40" t="s">
+        <v>49</v>
+      </c>
+      <c r="V40" t="s">
+        <v>49</v>
+      </c>
+      <c r="W40" t="s">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
+        <v>125</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" t="s">
+        <v>125</v>
+      </c>
+      <c r="H41" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" t="s">
+        <v>49</v>
+      </c>
+      <c r="N41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O41" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>49</v>
+      </c>
+      <c r="R41" t="s">
+        <v>76</v>
+      </c>
+      <c r="S41" t="s">
+        <v>49</v>
+      </c>
+      <c r="T41" t="s">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s">
+        <v>49</v>
+      </c>
+      <c r="V41" t="s">
+        <v>49</v>
+      </c>
+      <c r="W41" t="s">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" t="s">
+        <v>125</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" t="s">
+        <v>125</v>
+      </c>
+      <c r="H42" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" t="s">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" t="s">
+        <v>49</v>
+      </c>
+      <c r="M42" t="s">
+        <v>49</v>
+      </c>
+      <c r="N42" t="s">
+        <v>49</v>
+      </c>
+      <c r="O42" t="s">
+        <v>76</v>
+      </c>
+      <c r="P42" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>49</v>
+      </c>
+      <c r="R42" t="s">
+        <v>76</v>
+      </c>
+      <c r="S42" t="s">
+        <v>49</v>
+      </c>
+      <c r="T42" t="s">
+        <v>73</v>
+      </c>
+      <c r="U42" t="s">
+        <v>49</v>
+      </c>
+      <c r="V42" t="s">
+        <v>49</v>
+      </c>
+      <c r="W42" t="s">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" t="s">
+        <v>125</v>
+      </c>
+      <c r="H43" t="s">
+        <v>49</v>
+      </c>
+      <c r="I43" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43" t="s">
+        <v>75</v>
+      </c>
+      <c r="K43" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" t="s">
+        <v>49</v>
+      </c>
+      <c r="M43" t="s">
+        <v>49</v>
+      </c>
+      <c r="N43" t="s">
+        <v>49</v>
+      </c>
+      <c r="O43" t="s">
+        <v>76</v>
+      </c>
+      <c r="P43" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>49</v>
+      </c>
+      <c r="R43" t="s">
+        <v>76</v>
+      </c>
+      <c r="S43" t="s">
+        <v>49</v>
+      </c>
+      <c r="T43" t="s">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s">
+        <v>49</v>
+      </c>
+      <c r="V43" t="s">
+        <v>49</v>
+      </c>
+      <c r="W43" t="s">
+        <v>75</v>
+      </c>
+      <c r="X43" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" t="s">
+        <v>125</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" t="s">
+        <v>49</v>
+      </c>
+      <c r="M44" t="s">
+        <v>49</v>
+      </c>
+      <c r="N44" t="s">
+        <v>49</v>
+      </c>
+      <c r="O44" t="s">
+        <v>76</v>
+      </c>
+      <c r="P44" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>49</v>
+      </c>
+      <c r="R44" t="s">
+        <v>76</v>
+      </c>
+      <c r="S44" t="s">
+        <v>49</v>
+      </c>
+      <c r="T44" t="s">
+        <v>73</v>
+      </c>
+      <c r="U44" t="s">
+        <v>49</v>
+      </c>
+      <c r="V44" t="s">
+        <v>49</v>
+      </c>
+      <c r="W44" t="s">
+        <v>75</v>
+      </c>
+      <c r="X44" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H45" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J45" t="s">
+        <v>75</v>
+      </c>
+      <c r="K45" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" t="s">
+        <v>49</v>
+      </c>
+      <c r="O45" t="s">
+        <v>76</v>
+      </c>
+      <c r="P45" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>49</v>
+      </c>
+      <c r="R45" t="s">
+        <v>76</v>
+      </c>
+      <c r="S45" t="s">
+        <v>49</v>
+      </c>
+      <c r="T45" t="s">
+        <v>73</v>
+      </c>
+      <c r="U45" t="s">
+        <v>49</v>
+      </c>
+      <c r="V45" t="s">
+        <v>49</v>
+      </c>
+      <c r="W45" t="s">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" t="s">
+        <v>75</v>
+      </c>
+      <c r="J46" t="s">
+        <v>75</v>
+      </c>
+      <c r="K46" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" t="s">
+        <v>49</v>
+      </c>
+      <c r="M46" t="s">
+        <v>49</v>
+      </c>
+      <c r="N46" t="s">
+        <v>49</v>
+      </c>
+      <c r="O46" t="s">
+        <v>76</v>
+      </c>
+      <c r="P46" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>49</v>
+      </c>
+      <c r="R46" t="s">
+        <v>76</v>
+      </c>
+      <c r="S46" t="s">
+        <v>49</v>
+      </c>
+      <c r="T46" t="s">
+        <v>73</v>
+      </c>
+      <c r="U46" t="s">
+        <v>49</v>
+      </c>
+      <c r="V46" t="s">
+        <v>49</v>
+      </c>
+      <c r="W46" t="s">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G47" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
+        <v>75</v>
+      </c>
+      <c r="J47" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" t="s">
+        <v>49</v>
+      </c>
+      <c r="M47" t="s">
+        <v>49</v>
+      </c>
+      <c r="N47" t="s">
+        <v>49</v>
+      </c>
+      <c r="O47" t="s">
+        <v>76</v>
+      </c>
+      <c r="P47" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>49</v>
+      </c>
+      <c r="R47" t="s">
+        <v>76</v>
+      </c>
+      <c r="S47" t="s">
+        <v>49</v>
+      </c>
+      <c r="T47" t="s">
+        <v>73</v>
+      </c>
+      <c r="U47" t="s">
+        <v>49</v>
+      </c>
+      <c r="V47" t="s">
+        <v>49</v>
+      </c>
+      <c r="W47" t="s">
+        <v>75</v>
+      </c>
+      <c r="X47" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" t="s">
+        <v>125</v>
+      </c>
+      <c r="H48" t="s">
+        <v>49</v>
+      </c>
+      <c r="I48" t="s">
+        <v>75</v>
+      </c>
+      <c r="J48" t="s">
+        <v>75</v>
+      </c>
+      <c r="K48" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" t="s">
+        <v>49</v>
+      </c>
+      <c r="M48" t="s">
+        <v>49</v>
+      </c>
+      <c r="N48" t="s">
+        <v>49</v>
+      </c>
+      <c r="O48" t="s">
+        <v>76</v>
+      </c>
+      <c r="P48" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>49</v>
+      </c>
+      <c r="R48" t="s">
+        <v>76</v>
+      </c>
+      <c r="S48" t="s">
+        <v>49</v>
+      </c>
+      <c r="T48" t="s">
+        <v>73</v>
+      </c>
+      <c r="U48" t="s">
+        <v>49</v>
+      </c>
+      <c r="V48" t="s">
+        <v>49</v>
+      </c>
+      <c r="W48" t="s">
+        <v>75</v>
+      </c>
+      <c r="X48" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" t="s">
+        <v>131</v>
+      </c>
+      <c r="F49" t="s">
+        <v>131</v>
+      </c>
+      <c r="G49" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" t="s">
+        <v>75</v>
+      </c>
+      <c r="J49" t="s">
+        <v>75</v>
+      </c>
+      <c r="K49" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" t="s">
+        <v>49</v>
+      </c>
+      <c r="M49" t="s">
+        <v>49</v>
+      </c>
+      <c r="N49" t="s">
+        <v>49</v>
+      </c>
+      <c r="O49" t="s">
+        <v>76</v>
+      </c>
+      <c r="P49" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>49</v>
+      </c>
+      <c r="R49" t="s">
+        <v>76</v>
+      </c>
+      <c r="S49" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" t="s">
+        <v>73</v>
+      </c>
+      <c r="U49" t="s">
+        <v>49</v>
+      </c>
+      <c r="V49" t="s">
+        <v>49</v>
+      </c>
+      <c r="W49" t="s">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" t="s">
+        <v>126</v>
+      </c>
+      <c r="H50" t="s">
+        <v>49</v>
+      </c>
+      <c r="I50" t="s">
+        <v>75</v>
+      </c>
+      <c r="J50" t="s">
+        <v>75</v>
+      </c>
+      <c r="K50" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" t="s">
+        <v>49</v>
+      </c>
+      <c r="M50" t="s">
+        <v>49</v>
+      </c>
+      <c r="N50" t="s">
+        <v>49</v>
+      </c>
+      <c r="O50" t="s">
+        <v>76</v>
+      </c>
+      <c r="P50" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>49</v>
+      </c>
+      <c r="R50" t="s">
+        <v>76</v>
+      </c>
+      <c r="S50" t="s">
+        <v>49</v>
+      </c>
+      <c r="T50" t="s">
+        <v>73</v>
+      </c>
+      <c r="U50" t="s">
+        <v>49</v>
+      </c>
+      <c r="V50" t="s">
+        <v>49</v>
+      </c>
+      <c r="W50" t="s">
+        <v>75</v>
+      </c>
+      <c r="X50" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" t="s">
+        <v>125</v>
+      </c>
+      <c r="H51" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" t="s">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" t="s">
+        <v>49</v>
+      </c>
+      <c r="M51" t="s">
+        <v>49</v>
+      </c>
+      <c r="N51" t="s">
+        <v>49</v>
+      </c>
+      <c r="O51" t="s">
+        <v>76</v>
+      </c>
+      <c r="P51" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>49</v>
+      </c>
+      <c r="R51" t="s">
+        <v>76</v>
+      </c>
+      <c r="S51" t="s">
+        <v>49</v>
+      </c>
+      <c r="T51" t="s">
+        <v>73</v>
+      </c>
+      <c r="U51" t="s">
+        <v>49</v>
+      </c>
+      <c r="V51" t="s">
+        <v>49</v>
+      </c>
+      <c r="W51" t="s">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" t="s">
+        <v>131</v>
+      </c>
+      <c r="F52" t="s">
+        <v>131</v>
+      </c>
+      <c r="G52" t="s">
+        <v>126</v>
+      </c>
+      <c r="H52" t="s">
+        <v>49</v>
+      </c>
+      <c r="I52" t="s">
+        <v>75</v>
+      </c>
+      <c r="J52" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" t="s">
+        <v>49</v>
+      </c>
+      <c r="M52" t="s">
+        <v>49</v>
+      </c>
+      <c r="N52" t="s">
+        <v>49</v>
+      </c>
+      <c r="O52" t="s">
+        <v>76</v>
+      </c>
+      <c r="P52" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>49</v>
+      </c>
+      <c r="R52" t="s">
+        <v>76</v>
+      </c>
+      <c r="S52" t="s">
+        <v>49</v>
+      </c>
+      <c r="T52" t="s">
+        <v>73</v>
+      </c>
+      <c r="U52" t="s">
+        <v>49</v>
+      </c>
+      <c r="V52" t="s">
+        <v>49</v>
+      </c>
+      <c r="W52" t="s">
+        <v>75</v>
+      </c>
+      <c r="X52" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" t="s">
+        <v>131</v>
+      </c>
+      <c r="G53" t="s">
+        <v>126</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" t="s">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s">
+        <v>75</v>
+      </c>
+      <c r="K53" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" t="s">
+        <v>49</v>
+      </c>
+      <c r="M53" t="s">
+        <v>49</v>
+      </c>
+      <c r="N53" t="s">
+        <v>49</v>
+      </c>
+      <c r="O53" t="s">
+        <v>76</v>
+      </c>
+      <c r="P53" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>49</v>
+      </c>
+      <c r="R53" t="s">
+        <v>76</v>
+      </c>
+      <c r="S53" t="s">
+        <v>49</v>
+      </c>
+      <c r="T53" t="s">
+        <v>73</v>
+      </c>
+      <c r="U53" t="s">
+        <v>49</v>
+      </c>
+      <c r="V53" t="s">
+        <v>49</v>
+      </c>
+      <c r="W53" t="s">
+        <v>75</v>
+      </c>
+      <c r="X53" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" t="s">
+        <v>125</v>
+      </c>
+      <c r="H54" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" t="s">
+        <v>75</v>
+      </c>
+      <c r="J54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K54" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" t="s">
+        <v>49</v>
+      </c>
+      <c r="M54" t="s">
+        <v>49</v>
+      </c>
+      <c r="N54" t="s">
+        <v>49</v>
+      </c>
+      <c r="O54" t="s">
+        <v>76</v>
+      </c>
+      <c r="P54" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>49</v>
+      </c>
+      <c r="R54" t="s">
+        <v>76</v>
+      </c>
+      <c r="S54" t="s">
+        <v>49</v>
+      </c>
+      <c r="T54" t="s">
+        <v>73</v>
+      </c>
+      <c r="U54" t="s">
+        <v>49</v>
+      </c>
+      <c r="V54" t="s">
+        <v>49</v>
+      </c>
+      <c r="W54" t="s">
+        <v>75</v>
+      </c>
+      <c r="X54" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>62</v>
       </c>
-      <c r="D41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>18</v>
-      </c>
-      <c r="B45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>42</v>
-      </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G55" t="s">
+        <v>125</v>
+      </c>
+      <c r="H55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I55" t="s">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M55" t="s">
+        <v>49</v>
+      </c>
+      <c r="N55" t="s">
+        <v>49</v>
+      </c>
+      <c r="O55" t="s">
+        <v>76</v>
+      </c>
+      <c r="P55" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>49</v>
+      </c>
+      <c r="R55" t="s">
+        <v>76</v>
+      </c>
+      <c r="S55" t="s">
+        <v>49</v>
+      </c>
+      <c r="T55" t="s">
+        <v>73</v>
+      </c>
+      <c r="U55" t="s">
+        <v>49</v>
+      </c>
+      <c r="V55" t="s">
+        <v>49</v>
+      </c>
+      <c r="W55" t="s">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B58" s="1"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="1"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="1"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="E56" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
+        <v>49</v>
+      </c>
+      <c r="G56" t="s">
+        <v>125</v>
+      </c>
+      <c r="H56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I56" t="s">
+        <v>75</v>
+      </c>
+      <c r="J56" t="s">
+        <v>75</v>
+      </c>
+      <c r="K56" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" t="s">
+        <v>49</v>
+      </c>
+      <c r="M56" t="s">
+        <v>49</v>
+      </c>
+      <c r="N56" t="s">
+        <v>49</v>
+      </c>
+      <c r="O56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P56" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>49</v>
+      </c>
+      <c r="R56" t="s">
+        <v>76</v>
+      </c>
+      <c r="S56" t="s">
+        <v>49</v>
+      </c>
+      <c r="T56" t="s">
+        <v>73</v>
+      </c>
+      <c r="U56" t="s">
+        <v>49</v>
+      </c>
+      <c r="V56" t="s">
+        <v>49</v>
+      </c>
+      <c r="W56" t="s">
+        <v>75</v>
+      </c>
+      <c r="X56" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
+      <sortCondition ref="B1:B39"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A56">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1595,10 +5298,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C1" t="str">
         <f>"'"&amp;A1&amp;"': '"&amp;B1&amp;"',"</f>
@@ -1607,10 +5310,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" ref="C2:C22" si="0">"'"&amp;A2&amp;"': '"&amp;B2&amp;"',"</f>
@@ -1619,10 +5322,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
@@ -1631,10 +5334,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -1643,10 +5346,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -1655,10 +5358,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -1667,10 +5370,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -1679,10 +5382,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -1691,10 +5394,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -1703,10 +5406,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -1715,10 +5418,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -1727,7 +5430,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B12" t="str">
         <f>B1&amp;" - no onshore wind"</f>
@@ -1740,7 +5443,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" ref="B13:B22" si="1">B2&amp;" - no onshore wind"</f>
@@ -1753,7 +5456,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -1766,7 +5469,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -1779,7 +5482,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -1792,7 +5495,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -1805,7 +5508,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -1818,7 +5521,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -1831,7 +5534,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -1844,7 +5547,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -1857,7 +5560,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>

--- a/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
+++ b/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwiegner\PycharmProjects\AdOpT_DAC-Offshore\dac_offshore\clean_data\technologies_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D24750F-34C7-4616-9712-703932F086BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5015D0B1-7877-A040-A4B4-98ADA7200B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$F$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$N$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="133">
+  <si>
+    <t>Electrolyser_PEM_offshore</t>
+  </si>
   <si>
     <t>offshore_new</t>
   </si>
@@ -186,6 +189,9 @@
     <t>All</t>
   </si>
   <si>
+    <t>Offshore_Wind</t>
+  </si>
+  <si>
     <t>UK_L</t>
   </si>
   <si>
@@ -228,18 +234,51 @@
     <t>DE_G</t>
   </si>
   <si>
+    <t>New_Offshore_Farms_2040</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV</t>
+  </si>
+  <si>
+    <t>UK_M</t>
+  </si>
+  <si>
+    <t>UK_O</t>
+  </si>
+  <si>
+    <t>UK_N</t>
+  </si>
+  <si>
+    <t>Electrolyser_PEM_offshore, Storage_Battery_Offshore</t>
+  </si>
+  <si>
     <t>Onshore_Wind, PV, Storage_Battery_new</t>
   </si>
   <si>
+    <t>Onshore_Wind, PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen, Storage_Battery_new</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, Electrolyser_PEM_offshore, Storage_Battery_Offshore</t>
+  </si>
+  <si>
     <t>RE_only</t>
   </si>
   <si>
     <t>Offshore_Wind, Storage_Battery_Offshore</t>
   </si>
   <si>
+    <t>Offshore_Wind, Electrolyser_PEM_offshore</t>
+  </si>
+  <si>
     <t>All_no_onshore_wind</t>
   </si>
   <si>
+    <t>PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen, Storage_Battery_new</t>
+  </si>
+  <si>
     <t>RE_only_no_onshore_wind</t>
   </si>
   <si>
@@ -252,6 +291,15 @@
     <t>Hydrogen_Baseline_no_onshore_wind</t>
   </si>
   <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>PV, Storage_Battery_new</t>
+  </si>
+  <si>
+    <t>PV, Electrolyser_PEM, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
     <t>Battery_on</t>
   </si>
   <si>
@@ -270,6 +318,18 @@
     <t>Hydrogen_H4</t>
   </si>
   <si>
+    <t>Onshore_Wind, PV, Electrolyser_PEM, FuelCell</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
+    <t>PV, Electrolyser_PEM, FuelCell</t>
+  </si>
+  <si>
+    <t>PV, FuelCell, Storage_Hydrogen</t>
+  </si>
+  <si>
     <t>Battery_on_no_onshore_wind</t>
   </si>
   <si>
@@ -321,12 +381,30 @@
     <t>Hydrogen (local use only)</t>
   </si>
   <si>
+    <t>ElectricityGrid_on</t>
+  </si>
+  <si>
+    <t>ElectricityGrid_off</t>
+  </si>
+  <si>
+    <t>ElectricityGrid_noBorder</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
+  </si>
+  <si>
     <t>DK_ST1</t>
   </si>
   <si>
+    <t>New_CO2_Storage_2040</t>
+  </si>
+  <si>
     <t>NO_ST2</t>
   </si>
   <si>
+    <t>DK_ST2</t>
+  </si>
+  <si>
     <t>NO_ST1</t>
   </si>
   <si>
@@ -339,25 +417,28 @@
     <t>DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
   </si>
   <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
     <t>Offshore_DAC_only</t>
   </si>
   <si>
     <t>Onshore_DAC_only</t>
   </si>
   <si>
-    <t>DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
-  </si>
-  <si>
-    <t>No_DAC</t>
-  </si>
-  <si>
-    <t>co2storage</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Too far away for DAC</t>
+    <t>Onshore_DAC_retrofits</t>
+  </si>
+  <si>
+    <t>PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>RE_only_no_space</t>
   </si>
 </sst>
 </file>
@@ -400,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -408,40 +489,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -717,778 +789,4499 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="43" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="43" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" customWidth="1"/>
+    <col min="24" max="24" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>89</v>
+      </c>
+      <c r="R1" t="s">
+        <v>90</v>
+      </c>
+      <c r="S1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U1" t="str">
+        <f>C1&amp;"_no_onshore_wind"</f>
+        <v>RE_only_no_onshore_wind</v>
+      </c>
+      <c r="V1" t="str">
+        <f>H1&amp;"_no_onshore_wind"</f>
+        <v>Battery_on_no_onshore_wind</v>
+      </c>
+      <c r="W1" t="str">
+        <f>I1&amp;"_no_onshore_wind"</f>
+        <v>Battery_off_no_onshore_wind</v>
+      </c>
+      <c r="X1" t="str">
+        <f>J1&amp;"_no_onshore_wind"</f>
+        <v>Battery_all_no_onshore_wind</v>
+      </c>
+      <c r="Y1" t="str">
+        <f>K1&amp;"_no_onshore_wind"</f>
+        <v>ElectricityGrid_all_no_onshore_wind</v>
+      </c>
+      <c r="Z1" t="str">
+        <f t="shared" ref="Z1:AE1" si="0">O1&amp;"_no_onshore_wind"</f>
+        <v>Hydrogen_Baseline_no_onshore_wind</v>
+      </c>
+      <c r="AA1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H1_no_onshore_wind</v>
+      </c>
+      <c r="AB1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H2_no_onshore_wind</v>
+      </c>
+      <c r="AC1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H3_no_onshore_wind</v>
+      </c>
+      <c r="AD1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hydrogen_H4_no_onshore_wind</v>
+      </c>
+      <c r="AE1" t="str">
+        <f t="shared" si="0"/>
+        <v>All_no_onshore_wind</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>57</v>
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>0</v>
+      </c>
+      <c r="T9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W9" t="s">
+        <v>45</v>
+      </c>
+      <c r="X9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
+        <v>69</v>
+      </c>
+      <c r="W10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>122</v>
+      </c>
+      <c r="D11" t="s">
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>54</v>
+        <v>130</v>
+      </c>
+      <c r="F11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>69</v>
+      </c>
+      <c r="W11" t="s">
+        <v>45</v>
+      </c>
+      <c r="X11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>53</v>
+        <v>130</v>
+      </c>
+      <c r="F12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" t="s">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>69</v>
+      </c>
+      <c r="W12" t="s">
+        <v>45</v>
+      </c>
+      <c r="X12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" t="s">
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T13" t="s">
+        <v>69</v>
+      </c>
+      <c r="W13" t="s">
+        <v>45</v>
+      </c>
+      <c r="X13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>69</v>
+      </c>
+      <c r="W14" t="s">
+        <v>45</v>
+      </c>
+      <c r="X14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" t="s">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" t="s">
+        <v>69</v>
+      </c>
+      <c r="W15" t="s">
+        <v>45</v>
+      </c>
+      <c r="X15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>69</v>
+      </c>
+      <c r="W16" t="s">
+        <v>45</v>
+      </c>
+      <c r="X16" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" t="s">
+        <v>123</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
+        <v>69</v>
+      </c>
+      <c r="W17" t="s">
+        <v>45</v>
+      </c>
+      <c r="X17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
+        <v>69</v>
+      </c>
+      <c r="W18" t="s">
+        <v>45</v>
+      </c>
+      <c r="X18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>12</v>
+        <v>123</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" t="s">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
+        <v>69</v>
+      </c>
+      <c r="W19" t="s">
+        <v>45</v>
+      </c>
+      <c r="X19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>13</v>
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>0</v>
+      </c>
+      <c r="T20" t="s">
+        <v>69</v>
+      </c>
+      <c r="W20" t="s">
+        <v>45</v>
+      </c>
+      <c r="X20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" t="s">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
+        <v>0</v>
+      </c>
+      <c r="T21" t="s">
+        <v>69</v>
+      </c>
+      <c r="W21" t="s">
+        <v>45</v>
+      </c>
+      <c r="X21" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" t="s">
+        <v>123</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" t="s">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W22" t="s">
+        <v>45</v>
+      </c>
+      <c r="X22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O23" t="s">
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>0</v>
+      </c>
+      <c r="T23" t="s">
+        <v>69</v>
+      </c>
+      <c r="W23" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" t="s">
+        <v>70</v>
+      </c>
+      <c r="K24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" t="s">
+        <v>71</v>
+      </c>
+      <c r="P24" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>71</v>
+      </c>
+      <c r="R24" t="s">
+        <v>93</v>
+      </c>
+      <c r="S24" t="s">
+        <v>71</v>
+      </c>
+      <c r="T24" t="s">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s">
+        <v>83</v>
+      </c>
+      <c r="V24" t="s">
+        <v>84</v>
+      </c>
+      <c r="W24" t="s">
+        <v>83</v>
+      </c>
+      <c r="X24" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" t="s">
+        <v>70</v>
+      </c>
+      <c r="I25" t="s">
+        <v>65</v>
+      </c>
+      <c r="J25" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" t="s">
+        <v>71</v>
+      </c>
+      <c r="P25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>71</v>
+      </c>
+      <c r="R25" t="s">
+        <v>93</v>
+      </c>
+      <c r="S25" t="s">
+        <v>71</v>
+      </c>
+      <c r="T25" t="s">
+        <v>72</v>
+      </c>
+      <c r="U25" t="s">
+        <v>83</v>
+      </c>
+      <c r="V25" t="s">
+        <v>84</v>
+      </c>
+      <c r="W25" t="s">
+        <v>83</v>
+      </c>
+      <c r="X25" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" t="s">
+        <v>71</v>
+      </c>
+      <c r="P26" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>71</v>
+      </c>
+      <c r="R26" t="s">
+        <v>93</v>
+      </c>
+      <c r="S26" t="s">
+        <v>71</v>
+      </c>
+      <c r="T26" t="s">
+        <v>72</v>
+      </c>
+      <c r="U26" t="s">
+        <v>83</v>
+      </c>
+      <c r="V26" t="s">
+        <v>84</v>
+      </c>
+      <c r="W26" t="s">
+        <v>83</v>
+      </c>
+      <c r="X26" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>65</v>
+      </c>
+      <c r="N27" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" t="s">
+        <v>71</v>
+      </c>
+      <c r="P27" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>71</v>
+      </c>
+      <c r="R27" t="s">
+        <v>93</v>
+      </c>
+      <c r="S27" t="s">
+        <v>71</v>
+      </c>
+      <c r="T27" t="s">
+        <v>72</v>
+      </c>
+      <c r="U27" t="s">
+        <v>83</v>
+      </c>
+      <c r="V27" t="s">
+        <v>84</v>
+      </c>
+      <c r="W27" t="s">
+        <v>83</v>
+      </c>
+      <c r="X27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" t="s">
+        <v>65</v>
+      </c>
+      <c r="O28" t="s">
+        <v>71</v>
+      </c>
+      <c r="P28" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>71</v>
+      </c>
+      <c r="R28" t="s">
+        <v>93</v>
+      </c>
+      <c r="S28" t="s">
+        <v>71</v>
+      </c>
+      <c r="T28" t="s">
+        <v>72</v>
+      </c>
+      <c r="U28" t="s">
+        <v>83</v>
+      </c>
+      <c r="V28" t="s">
+        <v>84</v>
+      </c>
+      <c r="W28" t="s">
+        <v>83</v>
+      </c>
+      <c r="X28" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" t="s">
+        <v>70</v>
+      </c>
+      <c r="I29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P29" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" t="s">
+        <v>93</v>
+      </c>
+      <c r="S29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T29" t="s">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s">
+        <v>83</v>
+      </c>
+      <c r="V29" t="s">
+        <v>84</v>
+      </c>
+      <c r="W29" t="s">
+        <v>83</v>
+      </c>
+      <c r="X29" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" t="s">
+        <v>65</v>
+      </c>
+      <c r="O30" t="s">
+        <v>71</v>
+      </c>
+      <c r="P30" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30" t="s">
+        <v>93</v>
+      </c>
+      <c r="S30" t="s">
+        <v>71</v>
+      </c>
+      <c r="T30" t="s">
+        <v>72</v>
+      </c>
+      <c r="U30" t="s">
+        <v>83</v>
+      </c>
+      <c r="V30" t="s">
+        <v>84</v>
+      </c>
+      <c r="W30" t="s">
+        <v>83</v>
+      </c>
+      <c r="X30" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31" t="s">
+        <v>71</v>
+      </c>
+      <c r="P31" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>71</v>
+      </c>
+      <c r="R31" t="s">
+        <v>93</v>
+      </c>
+      <c r="S31" t="s">
+        <v>71</v>
+      </c>
+      <c r="T31" t="s">
+        <v>72</v>
+      </c>
+      <c r="U31" t="s">
+        <v>83</v>
+      </c>
+      <c r="V31" t="s">
+        <v>84</v>
+      </c>
+      <c r="W31" t="s">
+        <v>83</v>
+      </c>
+      <c r="X31" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32" t="s">
+        <v>71</v>
+      </c>
+      <c r="P32" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>71</v>
+      </c>
+      <c r="R32" t="s">
+        <v>93</v>
+      </c>
+      <c r="S32" t="s">
+        <v>71</v>
+      </c>
+      <c r="T32" t="s">
+        <v>72</v>
+      </c>
+      <c r="U32" t="s">
+        <v>83</v>
+      </c>
+      <c r="V32" t="s">
+        <v>84</v>
+      </c>
+      <c r="W32" t="s">
+        <v>83</v>
+      </c>
+      <c r="X32" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" t="s">
+        <v>70</v>
+      </c>
+      <c r="K33" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" t="s">
+        <v>65</v>
+      </c>
+      <c r="N33" t="s">
+        <v>65</v>
+      </c>
+      <c r="O33" t="s">
+        <v>71</v>
+      </c>
+      <c r="P33" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>71</v>
+      </c>
+      <c r="R33" t="s">
+        <v>93</v>
+      </c>
+      <c r="S33" t="s">
+        <v>71</v>
+      </c>
+      <c r="T33" t="s">
+        <v>72</v>
+      </c>
+      <c r="U33" t="s">
+        <v>83</v>
+      </c>
+      <c r="V33" t="s">
+        <v>84</v>
+      </c>
+      <c r="W33" t="s">
+        <v>83</v>
+      </c>
+      <c r="X33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" t="s">
+        <v>65</v>
+      </c>
+      <c r="O34" t="s">
+        <v>71</v>
+      </c>
+      <c r="P34" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>71</v>
+      </c>
+      <c r="R34" t="s">
+        <v>93</v>
+      </c>
+      <c r="S34" t="s">
+        <v>71</v>
+      </c>
+      <c r="T34" t="s">
+        <v>72</v>
+      </c>
+      <c r="U34" t="s">
+        <v>83</v>
+      </c>
+      <c r="V34" t="s">
+        <v>84</v>
+      </c>
+      <c r="W34" t="s">
+        <v>83</v>
+      </c>
+      <c r="X34" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" t="s">
+        <v>70</v>
+      </c>
+      <c r="I35" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" t="s">
+        <v>65</v>
+      </c>
+      <c r="O35" t="s">
+        <v>71</v>
+      </c>
+      <c r="P35" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>71</v>
+      </c>
+      <c r="R35" t="s">
+        <v>93</v>
+      </c>
+      <c r="S35" t="s">
+        <v>71</v>
+      </c>
+      <c r="T35" t="s">
+        <v>72</v>
+      </c>
+      <c r="U35" t="s">
+        <v>83</v>
+      </c>
+      <c r="V35" t="s">
+        <v>84</v>
+      </c>
+      <c r="W35" t="s">
+        <v>83</v>
+      </c>
+      <c r="X35" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I36" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" t="s">
+        <v>70</v>
+      </c>
+      <c r="K36" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" t="s">
+        <v>65</v>
+      </c>
+      <c r="N36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O36" t="s">
+        <v>71</v>
+      </c>
+      <c r="P36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>71</v>
+      </c>
+      <c r="R36" t="s">
+        <v>93</v>
+      </c>
+      <c r="S36" t="s">
+        <v>71</v>
+      </c>
+      <c r="T36" t="s">
+        <v>72</v>
+      </c>
+      <c r="U36" t="s">
+        <v>83</v>
+      </c>
+      <c r="V36" t="s">
+        <v>84</v>
+      </c>
+      <c r="W36" t="s">
+        <v>83</v>
+      </c>
+      <c r="X36" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" t="s">
+        <v>65</v>
+      </c>
+      <c r="O37" t="s">
+        <v>71</v>
+      </c>
+      <c r="P37" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>71</v>
+      </c>
+      <c r="R37" t="s">
+        <v>93</v>
+      </c>
+      <c r="S37" t="s">
+        <v>71</v>
+      </c>
+      <c r="T37" t="s">
+        <v>72</v>
+      </c>
+      <c r="U37" t="s">
+        <v>83</v>
+      </c>
+      <c r="V37" t="s">
+        <v>84</v>
+      </c>
+      <c r="W37" t="s">
+        <v>83</v>
+      </c>
+      <c r="X37" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" t="s">
+        <v>65</v>
+      </c>
+      <c r="N38" t="s">
+        <v>65</v>
+      </c>
+      <c r="O38" t="s">
+        <v>71</v>
+      </c>
+      <c r="P38" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>71</v>
+      </c>
+      <c r="R38" t="s">
+        <v>93</v>
+      </c>
+      <c r="S38" t="s">
+        <v>71</v>
+      </c>
+      <c r="T38" t="s">
+        <v>72</v>
+      </c>
+      <c r="U38" t="s">
+        <v>83</v>
+      </c>
+      <c r="V38" t="s">
+        <v>84</v>
+      </c>
+      <c r="W38" t="s">
+        <v>83</v>
+      </c>
+      <c r="X38" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>116</v>
+      </c>
+      <c r="D39" t="s">
+        <v>65</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>116</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" t="s">
+        <v>70</v>
+      </c>
+      <c r="K39" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" t="s">
+        <v>65</v>
+      </c>
+      <c r="N39" t="s">
+        <v>65</v>
+      </c>
+      <c r="O39" t="s">
+        <v>71</v>
+      </c>
+      <c r="P39" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>71</v>
+      </c>
+      <c r="R39" t="s">
+        <v>93</v>
+      </c>
+      <c r="S39" t="s">
+        <v>71</v>
+      </c>
+      <c r="T39" t="s">
+        <v>72</v>
+      </c>
+      <c r="U39" t="s">
+        <v>83</v>
+      </c>
+      <c r="V39" t="s">
+        <v>84</v>
+      </c>
+      <c r="W39" t="s">
+        <v>83</v>
+      </c>
+      <c r="X39" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>125</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" t="s">
+        <v>49</v>
+      </c>
+      <c r="I40" t="s">
+        <v>75</v>
+      </c>
+      <c r="J40" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" t="s">
+        <v>49</v>
+      </c>
+      <c r="M40" t="s">
+        <v>49</v>
+      </c>
+      <c r="N40" t="s">
+        <v>49</v>
+      </c>
+      <c r="O40" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>49</v>
+      </c>
+      <c r="R40" t="s">
+        <v>76</v>
+      </c>
+      <c r="S40" t="s">
+        <v>49</v>
+      </c>
+      <c r="T40" t="s">
+        <v>73</v>
+      </c>
+      <c r="U40" t="s">
+        <v>49</v>
+      </c>
+      <c r="V40" t="s">
+        <v>49</v>
+      </c>
+      <c r="W40" t="s">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
+        <v>125</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" t="s">
+        <v>125</v>
+      </c>
+      <c r="H41" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" t="s">
+        <v>49</v>
+      </c>
+      <c r="N41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O41" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>49</v>
+      </c>
+      <c r="R41" t="s">
+        <v>76</v>
+      </c>
+      <c r="S41" t="s">
+        <v>49</v>
+      </c>
+      <c r="T41" t="s">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s">
+        <v>49</v>
+      </c>
+      <c r="V41" t="s">
+        <v>49</v>
+      </c>
+      <c r="W41" t="s">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" t="s">
+        <v>125</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" t="s">
+        <v>125</v>
+      </c>
+      <c r="H42" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" t="s">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" t="s">
+        <v>49</v>
+      </c>
+      <c r="M42" t="s">
+        <v>49</v>
+      </c>
+      <c r="N42" t="s">
+        <v>49</v>
+      </c>
+      <c r="O42" t="s">
+        <v>76</v>
+      </c>
+      <c r="P42" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>49</v>
+      </c>
+      <c r="R42" t="s">
+        <v>76</v>
+      </c>
+      <c r="S42" t="s">
+        <v>49</v>
+      </c>
+      <c r="T42" t="s">
+        <v>73</v>
+      </c>
+      <c r="U42" t="s">
+        <v>49</v>
+      </c>
+      <c r="V42" t="s">
+        <v>49</v>
+      </c>
+      <c r="W42" t="s">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" t="s">
+        <v>125</v>
+      </c>
+      <c r="H43" t="s">
+        <v>49</v>
+      </c>
+      <c r="I43" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43" t="s">
+        <v>75</v>
+      </c>
+      <c r="K43" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" t="s">
+        <v>49</v>
+      </c>
+      <c r="M43" t="s">
+        <v>49</v>
+      </c>
+      <c r="N43" t="s">
+        <v>49</v>
+      </c>
+      <c r="O43" t="s">
+        <v>76</v>
+      </c>
+      <c r="P43" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>49</v>
+      </c>
+      <c r="R43" t="s">
+        <v>76</v>
+      </c>
+      <c r="S43" t="s">
+        <v>49</v>
+      </c>
+      <c r="T43" t="s">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s">
+        <v>49</v>
+      </c>
+      <c r="V43" t="s">
+        <v>49</v>
+      </c>
+      <c r="W43" t="s">
+        <v>75</v>
+      </c>
+      <c r="X43" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" t="s">
+        <v>125</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" t="s">
+        <v>49</v>
+      </c>
+      <c r="M44" t="s">
+        <v>49</v>
+      </c>
+      <c r="N44" t="s">
+        <v>49</v>
+      </c>
+      <c r="O44" t="s">
+        <v>76</v>
+      </c>
+      <c r="P44" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>49</v>
+      </c>
+      <c r="R44" t="s">
+        <v>76</v>
+      </c>
+      <c r="S44" t="s">
+        <v>49</v>
+      </c>
+      <c r="T44" t="s">
+        <v>73</v>
+      </c>
+      <c r="U44" t="s">
+        <v>49</v>
+      </c>
+      <c r="V44" t="s">
+        <v>49</v>
+      </c>
+      <c r="W44" t="s">
+        <v>75</v>
+      </c>
+      <c r="X44" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H45" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J45" t="s">
+        <v>75</v>
+      </c>
+      <c r="K45" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" t="s">
+        <v>49</v>
+      </c>
+      <c r="O45" t="s">
+        <v>76</v>
+      </c>
+      <c r="P45" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>49</v>
+      </c>
+      <c r="R45" t="s">
+        <v>76</v>
+      </c>
+      <c r="S45" t="s">
+        <v>49</v>
+      </c>
+      <c r="T45" t="s">
+        <v>73</v>
+      </c>
+      <c r="U45" t="s">
+        <v>49</v>
+      </c>
+      <c r="V45" t="s">
+        <v>49</v>
+      </c>
+      <c r="W45" t="s">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" t="s">
+        <v>75</v>
+      </c>
+      <c r="J46" t="s">
+        <v>75</v>
+      </c>
+      <c r="K46" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" t="s">
+        <v>49</v>
+      </c>
+      <c r="M46" t="s">
+        <v>49</v>
+      </c>
+      <c r="N46" t="s">
+        <v>49</v>
+      </c>
+      <c r="O46" t="s">
+        <v>76</v>
+      </c>
+      <c r="P46" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>49</v>
+      </c>
+      <c r="R46" t="s">
+        <v>76</v>
+      </c>
+      <c r="S46" t="s">
+        <v>49</v>
+      </c>
+      <c r="T46" t="s">
+        <v>73</v>
+      </c>
+      <c r="U46" t="s">
+        <v>49</v>
+      </c>
+      <c r="V46" t="s">
+        <v>49</v>
+      </c>
+      <c r="W46" t="s">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G47" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
+        <v>75</v>
+      </c>
+      <c r="J47" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" t="s">
+        <v>49</v>
+      </c>
+      <c r="M47" t="s">
+        <v>49</v>
+      </c>
+      <c r="N47" t="s">
+        <v>49</v>
+      </c>
+      <c r="O47" t="s">
+        <v>76</v>
+      </c>
+      <c r="P47" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>49</v>
+      </c>
+      <c r="R47" t="s">
+        <v>76</v>
+      </c>
+      <c r="S47" t="s">
+        <v>49</v>
+      </c>
+      <c r="T47" t="s">
+        <v>73</v>
+      </c>
+      <c r="U47" t="s">
+        <v>49</v>
+      </c>
+      <c r="V47" t="s">
+        <v>49</v>
+      </c>
+      <c r="W47" t="s">
+        <v>75</v>
+      </c>
+      <c r="X47" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" t="s">
+        <v>125</v>
+      </c>
+      <c r="H48" t="s">
+        <v>49</v>
+      </c>
+      <c r="I48" t="s">
+        <v>75</v>
+      </c>
+      <c r="J48" t="s">
+        <v>75</v>
+      </c>
+      <c r="K48" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" t="s">
+        <v>49</v>
+      </c>
+      <c r="M48" t="s">
+        <v>49</v>
+      </c>
+      <c r="N48" t="s">
+        <v>49</v>
+      </c>
+      <c r="O48" t="s">
+        <v>76</v>
+      </c>
+      <c r="P48" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>49</v>
+      </c>
+      <c r="R48" t="s">
+        <v>76</v>
+      </c>
+      <c r="S48" t="s">
+        <v>49</v>
+      </c>
+      <c r="T48" t="s">
+        <v>73</v>
+      </c>
+      <c r="U48" t="s">
+        <v>49</v>
+      </c>
+      <c r="V48" t="s">
+        <v>49</v>
+      </c>
+      <c r="W48" t="s">
+        <v>75</v>
+      </c>
+      <c r="X48" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" t="s">
+        <v>131</v>
+      </c>
+      <c r="F49" t="s">
+        <v>131</v>
+      </c>
+      <c r="G49" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" t="s">
+        <v>75</v>
+      </c>
+      <c r="J49" t="s">
+        <v>75</v>
+      </c>
+      <c r="K49" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" t="s">
+        <v>49</v>
+      </c>
+      <c r="M49" t="s">
+        <v>49</v>
+      </c>
+      <c r="N49" t="s">
+        <v>49</v>
+      </c>
+      <c r="O49" t="s">
+        <v>76</v>
+      </c>
+      <c r="P49" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>49</v>
+      </c>
+      <c r="R49" t="s">
+        <v>76</v>
+      </c>
+      <c r="S49" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" t="s">
+        <v>73</v>
+      </c>
+      <c r="U49" t="s">
+        <v>49</v>
+      </c>
+      <c r="V49" t="s">
+        <v>49</v>
+      </c>
+      <c r="W49" t="s">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" t="s">
+        <v>126</v>
+      </c>
+      <c r="H50" t="s">
+        <v>49</v>
+      </c>
+      <c r="I50" t="s">
+        <v>75</v>
+      </c>
+      <c r="J50" t="s">
+        <v>75</v>
+      </c>
+      <c r="K50" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" t="s">
+        <v>49</v>
+      </c>
+      <c r="M50" t="s">
+        <v>49</v>
+      </c>
+      <c r="N50" t="s">
+        <v>49</v>
+      </c>
+      <c r="O50" t="s">
+        <v>76</v>
+      </c>
+      <c r="P50" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>49</v>
+      </c>
+      <c r="R50" t="s">
+        <v>76</v>
+      </c>
+      <c r="S50" t="s">
+        <v>49</v>
+      </c>
+      <c r="T50" t="s">
+        <v>73</v>
+      </c>
+      <c r="U50" t="s">
+        <v>49</v>
+      </c>
+      <c r="V50" t="s">
+        <v>49</v>
+      </c>
+      <c r="W50" t="s">
+        <v>75</v>
+      </c>
+      <c r="X50" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" t="s">
+        <v>125</v>
+      </c>
+      <c r="H51" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" t="s">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" t="s">
+        <v>49</v>
+      </c>
+      <c r="M51" t="s">
+        <v>49</v>
+      </c>
+      <c r="N51" t="s">
+        <v>49</v>
+      </c>
+      <c r="O51" t="s">
+        <v>76</v>
+      </c>
+      <c r="P51" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>49</v>
+      </c>
+      <c r="R51" t="s">
+        <v>76</v>
+      </c>
+      <c r="S51" t="s">
+        <v>49</v>
+      </c>
+      <c r="T51" t="s">
+        <v>73</v>
+      </c>
+      <c r="U51" t="s">
+        <v>49</v>
+      </c>
+      <c r="V51" t="s">
+        <v>49</v>
+      </c>
+      <c r="W51" t="s">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" t="s">
+        <v>131</v>
+      </c>
+      <c r="F52" t="s">
+        <v>131</v>
+      </c>
+      <c r="G52" t="s">
+        <v>126</v>
+      </c>
+      <c r="H52" t="s">
+        <v>49</v>
+      </c>
+      <c r="I52" t="s">
+        <v>75</v>
+      </c>
+      <c r="J52" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" t="s">
+        <v>49</v>
+      </c>
+      <c r="M52" t="s">
+        <v>49</v>
+      </c>
+      <c r="N52" t="s">
+        <v>49</v>
+      </c>
+      <c r="O52" t="s">
+        <v>76</v>
+      </c>
+      <c r="P52" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>49</v>
+      </c>
+      <c r="R52" t="s">
+        <v>76</v>
+      </c>
+      <c r="S52" t="s">
+        <v>49</v>
+      </c>
+      <c r="T52" t="s">
+        <v>73</v>
+      </c>
+      <c r="U52" t="s">
+        <v>49</v>
+      </c>
+      <c r="V52" t="s">
+        <v>49</v>
+      </c>
+      <c r="W52" t="s">
+        <v>75</v>
+      </c>
+      <c r="X52" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" t="s">
+        <v>131</v>
+      </c>
+      <c r="G53" t="s">
+        <v>126</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" t="s">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s">
+        <v>75</v>
+      </c>
+      <c r="K53" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" t="s">
+        <v>49</v>
+      </c>
+      <c r="M53" t="s">
+        <v>49</v>
+      </c>
+      <c r="N53" t="s">
+        <v>49</v>
+      </c>
+      <c r="O53" t="s">
+        <v>76</v>
+      </c>
+      <c r="P53" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>49</v>
+      </c>
+      <c r="R53" t="s">
+        <v>76</v>
+      </c>
+      <c r="S53" t="s">
+        <v>49</v>
+      </c>
+      <c r="T53" t="s">
+        <v>73</v>
+      </c>
+      <c r="U53" t="s">
+        <v>49</v>
+      </c>
+      <c r="V53" t="s">
+        <v>49</v>
+      </c>
+      <c r="W53" t="s">
+        <v>75</v>
+      </c>
+      <c r="X53" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" t="s">
+        <v>125</v>
+      </c>
+      <c r="H54" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" t="s">
+        <v>75</v>
+      </c>
+      <c r="J54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K54" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" t="s">
+        <v>49</v>
+      </c>
+      <c r="M54" t="s">
+        <v>49</v>
+      </c>
+      <c r="N54" t="s">
+        <v>49</v>
+      </c>
+      <c r="O54" t="s">
+        <v>76</v>
+      </c>
+      <c r="P54" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>49</v>
+      </c>
+      <c r="R54" t="s">
+        <v>76</v>
+      </c>
+      <c r="S54" t="s">
+        <v>49</v>
+      </c>
+      <c r="T54" t="s">
+        <v>73</v>
+      </c>
+      <c r="U54" t="s">
+        <v>49</v>
+      </c>
+      <c r="V54" t="s">
+        <v>49</v>
+      </c>
+      <c r="W54" t="s">
+        <v>75</v>
+      </c>
+      <c r="X54" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>62</v>
       </c>
-      <c r="D41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>18</v>
-      </c>
-      <c r="B45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>42</v>
-      </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G55" t="s">
+        <v>125</v>
+      </c>
+      <c r="H55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I55" t="s">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M55" t="s">
+        <v>49</v>
+      </c>
+      <c r="N55" t="s">
+        <v>49</v>
+      </c>
+      <c r="O55" t="s">
+        <v>76</v>
+      </c>
+      <c r="P55" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>49</v>
+      </c>
+      <c r="R55" t="s">
+        <v>76</v>
+      </c>
+      <c r="S55" t="s">
+        <v>49</v>
+      </c>
+      <c r="T55" t="s">
+        <v>73</v>
+      </c>
+      <c r="U55" t="s">
+        <v>49</v>
+      </c>
+      <c r="V55" t="s">
+        <v>49</v>
+      </c>
+      <c r="W55" t="s">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>125</v>
+      </c>
+      <c r="E56" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
+        <v>49</v>
+      </c>
+      <c r="G56" t="s">
+        <v>125</v>
+      </c>
+      <c r="H56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I56" t="s">
+        <v>75</v>
+      </c>
+      <c r="J56" t="s">
+        <v>75</v>
+      </c>
+      <c r="K56" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" t="s">
+        <v>49</v>
+      </c>
+      <c r="M56" t="s">
+        <v>49</v>
+      </c>
+      <c r="N56" t="s">
+        <v>49</v>
+      </c>
+      <c r="O56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P56" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>49</v>
+      </c>
+      <c r="R56" t="s">
+        <v>76</v>
+      </c>
+      <c r="S56" t="s">
+        <v>49</v>
+      </c>
+      <c r="T56" t="s">
+        <v>73</v>
+      </c>
+      <c r="U56" t="s">
+        <v>49</v>
+      </c>
+      <c r="V56" t="s">
+        <v>49</v>
+      </c>
+      <c r="W56" t="s">
+        <v>75</v>
+      </c>
+      <c r="X56" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F56" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
+      <sortCondition ref="B1:B39"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1497,147 +5290,147 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4641E15-13AD-4645-88BC-55D8D2E876ED}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C1" t="str">
         <f>"'"&amp;A1&amp;"': '"&amp;B1&amp;"',"</f>
         <v>'RE_only': 'RE only',</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" ref="C2:C22" si="0">"'"&amp;A2&amp;"': '"&amp;B2&amp;"',"</f>
         <v>'Battery_on': 'Battery (onshore only)',</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
         <v>'Battery_off': 'Battery (offshore only)',</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
         <v>'Battery_all': 'Battery (all)',</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
         <v>'ElectricityGrid_all': 'Grid Expansion (all)',</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
         <v>'Hydrogen_Baseline': 'Hydrogen (all)',</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
         <v>'Hydrogen_H1': 'Hydrogen (no storage)',</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
         <v>'Hydrogen_H2': 'Hydrogen (no hydrogen offshore)',</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
         <v>'Hydrogen_H3': 'Hydrogen (no hydrogen onshore)',</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
         <v>'Hydrogen_H4': 'Hydrogen (local use only)',</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
         <v>'All': 'All Pathways',</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B12" t="str">
         <f>B1&amp;" - no onshore wind"</f>
@@ -1648,9 +5441,9 @@
         <v>'RE_only_no_onshore_wind': 'RE only - no onshore wind',</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" ref="B13:B22" si="1">B2&amp;" - no onshore wind"</f>
@@ -1661,9 +5454,9 @@
         <v>'Battery_on_no_onshore_wind': 'Battery (onshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
@@ -1674,9 +5467,9 @@
         <v>'Battery_off_no_onshore_wind': 'Battery (offshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
@@ -1687,9 +5480,9 @@
         <v>'Battery_all_no_onshore_wind': 'Battery (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
@@ -1700,9 +5493,9 @@
         <v>'ElectricityGrid_all_no_onshore_wind': 'Grid Expansion (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
@@ -1713,9 +5506,9 @@
         <v>'Hydrogen_Baseline_no_onshore_wind': 'Hydrogen (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
@@ -1726,9 +5519,9 @@
         <v>'Hydrogen_H1_no_onshore_wind': 'Hydrogen (no storage) - no onshore wind',</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
@@ -1739,9 +5532,9 @@
         <v>'Hydrogen_H2_no_onshore_wind': 'Hydrogen (no hydrogen offshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
@@ -1752,9 +5545,9 @@
         <v>'Hydrogen_H3_no_onshore_wind': 'Hydrogen (no hydrogen onshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
@@ -1765,9 +5558,9 @@
         <v>'Hydrogen_H4_no_onshore_wind': 'Hydrogen (local use only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>

--- a/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
+++ b/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/AdOpT-NET0_DAC-Offshore/dac_offshore/clean_data/technologies_new/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/8051917/PycharmProjects/AdOpT-NET0_DAC-Offshore/dac_offshore/clean_data/technologies_new/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B970953-C56B-E842-9483-313AFEB9052B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840FCBE4-6471-B74F-8744-38094E7F9480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="105">
   <si>
     <t>offshore_new</t>
   </si>
@@ -330,15 +330,9 @@
     <t>NO_ST1</t>
   </si>
   <si>
-    <t>PermanentStorage_CO2_simple, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
-  </si>
-  <si>
     <t>DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
   </si>
   <si>
-    <t>DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
-  </si>
-  <si>
     <t>Offshore_DAC_only</t>
   </si>
   <si>
@@ -355,6 +349,12 @@
   </si>
   <si>
     <t>DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, Storage_Battery_Offshore, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Storage_Battery_Offshore, PermanentStorage_CO2_simple</t>
   </si>
 </sst>
 </file>
@@ -731,7 +731,9 @@
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="24" customWidth="1"/>
+    <col min="3" max="3" width="49.1640625" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" customWidth="1"/>
+    <col min="5" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="15.33203125" customWidth="1"/>
     <col min="15" max="15" width="43" bestFit="1" customWidth="1"/>
@@ -751,13 +753,13 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -765,10 +767,10 @@
         <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" t="s">
         <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>96</v>
@@ -779,10 +781,10 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
         <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>96</v>
@@ -793,10 +795,10 @@
         <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
         <v>101</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>96</v>
@@ -813,7 +815,7 @@
         <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -827,7 +829,7 @@
         <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -841,7 +843,7 @@
         <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -852,13 +854,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -869,13 +868,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -891,7 +887,7 @@
         <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -902,13 +898,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -919,13 +912,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -939,7 +929,7 @@
         <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -952,13 +942,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -972,7 +959,7 @@
         <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -986,7 +973,7 @@
         <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1000,7 +987,7 @@
         <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1014,7 +1001,7 @@
         <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1102,12 +1089,9 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1130,10 +1114,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
         <v>96</v>
@@ -1147,10 +1128,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
         <v>96</v>
@@ -1164,12 +1142,9 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1184,7 +1159,7 @@
         <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1198,7 +1173,7 @@
         <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1212,7 +1187,7 @@
         <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1226,7 +1201,7 @@
         <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1240,7 +1215,7 @@
         <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1254,7 +1229,7 @@
         <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1265,13 +1240,10 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E37" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1282,13 +1254,10 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1302,7 +1271,7 @@
         <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1313,13 +1282,10 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1333,7 +1299,7 @@
         <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1347,7 +1313,7 @@
         <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1361,7 +1327,7 @@
         <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1375,7 +1341,7 @@
         <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1389,7 +1355,7 @@
         <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1403,7 +1369,7 @@
         <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1417,7 +1383,7 @@
         <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1431,7 +1397,7 @@
         <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -1445,7 +1411,7 @@
         <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -1459,7 +1425,7 @@
         <v>62</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -1473,7 +1439,7 @@
         <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -1487,7 +1453,7 @@
         <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -1501,7 +1467,7 @@
         <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -1515,7 +1481,7 @@
         <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -1529,7 +1495,7 @@
         <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -1543,7 +1509,7 @@
         <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">

--- a/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
+++ b/dac_offshore/clean_data/technologies_new/NewTechnologies.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/8051917/PycharmProjects/AdOpT-NET0_DAC-Offshore/dac_offshore/clean_data/technologies_new/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwiegner\PycharmProjects\AdOpT_DAC-Offshore\dac_offshore\clean_data\technologies_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840FCBE4-6471-B74F-8744-38094E7F9480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1E4727-1253-4B73-BAD7-E91EAC044CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="-21720" yWindow="-1965" windowWidth="21840" windowHeight="37920" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$O$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="104">
   <si>
     <t>offshore_new</t>
   </si>
@@ -351,10 +351,7 @@
     <t>DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
   </si>
   <si>
-    <t>Offshore_Wind, Storage_Battery_Offshore, PermanentStorage_CO2_simple</t>
-  </si>
-  <si>
-    <t>Storage_Battery_Offshore, PermanentStorage_CO2_simple</t>
+    <t>CO2_Storage</t>
   </si>
 </sst>
 </file>
@@ -726,26 +723,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.1640625" customWidth="1"/>
-    <col min="4" max="4" width="40.1640625" customWidth="1"/>
-    <col min="5" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="43" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="43" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="15.33203125" customWidth="1"/>
-    <col min="24" max="24" width="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="49.140625" customWidth="1"/>
+    <col min="5" max="5" width="40.140625" customWidth="1"/>
+    <col min="6" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="43" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="43" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24" customWidth="1"/>
+    <col min="23" max="23" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -756,55 +753,58 @@
         <v>100</v>
       </c>
       <c r="D1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
       <c r="B2" t="s">
         <v>101</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>99</v>
       </c>
-      <c r="E2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>95</v>
       </c>
       <c r="B3" t="s">
         <v>101</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>99</v>
       </c>
-      <c r="E3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>94</v>
       </c>
       <c r="B4" t="s">
         <v>101</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>99</v>
       </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -814,11 +814,11 @@
       <c r="C5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -828,11 +828,11 @@
       <c r="C6" t="s">
         <v>64</v>
       </c>
-      <c r="E6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -842,11 +842,11 @@
       <c r="C7" t="s">
         <v>64</v>
       </c>
-      <c r="E7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -854,13 +854,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -868,15 +871,18 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" t="s">
+        <v>96</v>
+      </c>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -886,11 +892,11 @@
       <c r="C10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -898,13 +904,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -912,13 +921,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -928,13 +940,13 @@
       <c r="C13" t="s">
         <v>64</v>
       </c>
-      <c r="E13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="2"/>
+      <c r="F13" t="s">
+        <v>96</v>
+      </c>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -942,13 +954,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -958,11 +973,11 @@
       <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="E15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -972,11 +987,11 @@
       <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="E16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -986,11 +1001,11 @@
       <c r="C17" t="s">
         <v>64</v>
       </c>
-      <c r="E17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1000,11 +1015,11 @@
       <c r="C18" t="s">
         <v>64</v>
       </c>
-      <c r="E18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1015,7 +1030,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1026,7 +1041,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1037,7 +1052,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1048,7 +1063,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1059,7 +1074,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1070,7 +1085,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1081,7 +1096,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
@@ -1089,13 +1104,16 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1106,7 +1124,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
@@ -1114,13 +1132,16 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
@@ -1128,13 +1149,16 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
@@ -1142,13 +1166,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1158,11 +1185,11 @@
       <c r="C31" t="s">
         <v>44</v>
       </c>
-      <c r="E31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1172,11 +1199,11 @@
       <c r="C32" t="s">
         <v>44</v>
       </c>
-      <c r="E32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -1186,11 +1213,11 @@
       <c r="C33" t="s">
         <v>44</v>
       </c>
-      <c r="E33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -1200,11 +1227,11 @@
       <c r="C34" t="s">
         <v>44</v>
       </c>
-      <c r="E34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -1214,11 +1241,11 @@
       <c r="C35" t="s">
         <v>44</v>
       </c>
-      <c r="E35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -1228,11 +1255,11 @@
       <c r="C36" t="s">
         <v>44</v>
       </c>
-      <c r="E36" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>33</v>
       </c>
@@ -1240,13 +1267,16 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>34</v>
       </c>
@@ -1254,13 +1284,16 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -1270,11 +1303,11 @@
       <c r="C39" t="s">
         <v>44</v>
       </c>
-      <c r="E39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>36</v>
       </c>
@@ -1282,13 +1315,16 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1298,11 +1334,11 @@
       <c r="C41" t="s">
         <v>62</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -1312,11 +1348,11 @@
       <c r="C42" t="s">
         <v>62</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -1326,11 +1362,11 @@
       <c r="C43" t="s">
         <v>62</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1340,11 +1376,11 @@
       <c r="C44" t="s">
         <v>62</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1354,11 +1390,11 @@
       <c r="C45" t="s">
         <v>62</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1368,11 +1404,11 @@
       <c r="C46" t="s">
         <v>62</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1382,11 +1418,11 @@
       <c r="C47" t="s">
         <v>62</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -1396,11 +1432,11 @@
       <c r="C48" t="s">
         <v>62</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -1410,11 +1446,11 @@
       <c r="C49" t="s">
         <v>62</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -1424,11 +1460,11 @@
       <c r="C50" t="s">
         <v>62</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -1438,11 +1474,11 @@
       <c r="C51" t="s">
         <v>62</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -1452,11 +1488,11 @@
       <c r="C52" t="s">
         <v>62</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -1466,11 +1502,11 @@
       <c r="C53" t="s">
         <v>62</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>41</v>
       </c>
@@ -1480,11 +1516,11 @@
       <c r="C54" t="s">
         <v>62</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -1494,11 +1530,11 @@
       <c r="C55" t="s">
         <v>62</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>43</v>
       </c>
@@ -1508,36 +1544,39 @@
       <c r="C56" t="s">
         <v>62</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1553,13 +1592,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4641E15-13AD-4645-88BC-55D8D2E876ED}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -1571,7 +1610,7 @@
         <v>'RE_only': 'RE only',</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1583,7 +1622,7 @@
         <v>'Battery_on': 'Battery (onshore only)',</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1595,7 +1634,7 @@
         <v>'Battery_off': 'Battery (offshore only)',</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1607,7 +1646,7 @@
         <v>'Battery_all': 'Battery (all)',</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1619,7 +1658,7 @@
         <v>'ElectricityGrid_all': 'Grid Expansion (all)',</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1631,7 +1670,7 @@
         <v>'Hydrogen_Baseline': 'Hydrogen (all)',</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -1643,7 +1682,7 @@
         <v>'Hydrogen_H1': 'Hydrogen (no storage)',</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -1655,7 +1694,7 @@
         <v>'Hydrogen_H2': 'Hydrogen (no hydrogen offshore)',</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
@@ -1667,7 +1706,7 @@
         <v>'Hydrogen_H3': 'Hydrogen (no hydrogen onshore)',</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -1679,7 +1718,7 @@
         <v>'Hydrogen_H4': 'Hydrogen (local use only)',</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1691,7 +1730,7 @@
         <v>'All': 'All Pathways',</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -1704,7 +1743,7 @@
         <v>'RE_only_no_onshore_wind': 'RE only - no onshore wind',</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -1717,7 +1756,7 @@
         <v>'Battery_on_no_onshore_wind': 'Battery (onshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>77</v>
       </c>
@@ -1730,7 +1769,7 @@
         <v>'Battery_off_no_onshore_wind': 'Battery (offshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -1743,7 +1782,7 @@
         <v>'Battery_all_no_onshore_wind': 'Battery (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1756,7 +1795,7 @@
         <v>'ElectricityGrid_all_no_onshore_wind': 'Grid Expansion (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -1769,7 +1808,7 @@
         <v>'Hydrogen_Baseline_no_onshore_wind': 'Hydrogen (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>78</v>
       </c>
@@ -1782,7 +1821,7 @@
         <v>'Hydrogen_H1_no_onshore_wind': 'Hydrogen (no storage) - no onshore wind',</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -1795,7 +1834,7 @@
         <v>'Hydrogen_H2_no_onshore_wind': 'Hydrogen (no hydrogen offshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -1808,7 +1847,7 @@
         <v>'Hydrogen_H3_no_onshore_wind': 'Hydrogen (no hydrogen onshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -1821,7 +1860,7 @@
         <v>'Hydrogen_H4_no_onshore_wind': 'Hydrogen (local use only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
